--- a/ReservingProject.xlsx
+++ b/ReservingProject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tyler\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CE21868-22FB-4F73-90F2-C81CB6C270F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D95E7328-C530-4C42-9AD1-838B747462C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{44F31B50-3BBF-4442-BC18-6E6AFA416118}"/>
   </bookViews>
@@ -24,6 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlcn.WorksheetConnection_Book1Table11" hidden="1">Table1[]</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">Comparison!$A$1:$Q$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -119,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="71">
   <si>
     <t>GRCODE</t>
   </si>
@@ -741,7 +742,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -767,7 +768,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -780,7 +780,6 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
@@ -815,6 +814,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -824,6 +824,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -4842,96 +4848,97 @@
   <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="123.85546875" style="68" customWidth="1"/>
+    <col min="1" max="1" width="123.85546875" style="66" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="72" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="66" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="72" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="66" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="72" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="66" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="72" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="66" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="72" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="66" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="73" t="s">
+      <c r="A18" s="72" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="66" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A21" s="73" t="s">
+      <c r="A21" s="72" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="68" t="s">
+      <c r="A22" s="66" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A24" s="73" t="s">
+      <c r="A24" s="72" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="68" t="s">
+      <c r="A25" s="66" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9574,34 +9581,34 @@
       <c r="A5" s="11">
         <v>1998</v>
       </c>
-      <c r="B5" s="70">
+      <c r="B5" s="69">
         <v>65419</v>
       </c>
-      <c r="C5" s="71">
+      <c r="C5" s="70">
         <v>102612</v>
       </c>
-      <c r="D5" s="71">
+      <c r="D5" s="70">
         <v>114906</v>
       </c>
-      <c r="E5" s="71">
+      <c r="E5" s="70">
         <v>121101</v>
       </c>
-      <c r="F5" s="71">
+      <c r="F5" s="70">
         <v>123407</v>
       </c>
-      <c r="G5" s="71">
+      <c r="G5" s="70">
         <v>124722</v>
       </c>
-      <c r="H5" s="71">
+      <c r="H5" s="70">
         <v>125342</v>
       </c>
-      <c r="I5" s="71">
+      <c r="I5" s="70">
         <v>125794</v>
       </c>
-      <c r="J5" s="71">
+      <c r="J5" s="70">
         <v>125933</v>
       </c>
-      <c r="K5" s="72">
+      <c r="K5" s="71">
         <v>126038</v>
       </c>
     </row>
@@ -9609,31 +9616,31 @@
       <c r="A6" s="11">
         <v>1999</v>
       </c>
-      <c r="B6" s="70">
+      <c r="B6" s="69">
         <v>74601</v>
       </c>
-      <c r="C6" s="71">
+      <c r="C6" s="70">
         <v>114612</v>
       </c>
-      <c r="D6" s="71">
+      <c r="D6" s="70">
         <v>126195</v>
       </c>
-      <c r="E6" s="71">
+      <c r="E6" s="70">
         <v>132596</v>
       </c>
-      <c r="F6" s="71">
+      <c r="F6" s="70">
         <v>135336</v>
       </c>
-      <c r="G6" s="71">
+      <c r="G6" s="70">
         <v>136351</v>
       </c>
-      <c r="H6" s="71">
+      <c r="H6" s="70">
         <v>136714</v>
       </c>
-      <c r="I6" s="71">
+      <c r="I6" s="70">
         <v>137108</v>
       </c>
-      <c r="J6" s="72">
+      <c r="J6" s="71">
         <v>137247</v>
       </c>
       <c r="K6" s="8"/>
@@ -9642,28 +9649,28 @@
       <c r="A7" s="11">
         <v>2000</v>
       </c>
-      <c r="B7" s="70">
+      <c r="B7" s="69">
         <v>76960</v>
       </c>
-      <c r="C7" s="71">
+      <c r="C7" s="70">
         <v>119712</v>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="70">
         <v>130613</v>
       </c>
-      <c r="E7" s="71">
+      <c r="E7" s="70">
         <v>137202</v>
       </c>
-      <c r="F7" s="71">
+      <c r="F7" s="70">
         <v>139337</v>
       </c>
-      <c r="G7" s="71">
+      <c r="G7" s="70">
         <v>140522</v>
       </c>
-      <c r="H7" s="71">
+      <c r="H7" s="70">
         <v>141045</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="71">
         <v>141264</v>
       </c>
       <c r="J7" s="8"/>
@@ -9673,25 +9680,25 @@
       <c r="A8" s="11">
         <v>2001</v>
       </c>
-      <c r="B8" s="70">
+      <c r="B8" s="69">
         <v>79831</v>
       </c>
-      <c r="C8" s="71">
+      <c r="C8" s="70">
         <v>120247</v>
       </c>
-      <c r="D8" s="71">
+      <c r="D8" s="70">
         <v>131574</v>
       </c>
-      <c r="E8" s="71">
+      <c r="E8" s="70">
         <v>137030</v>
       </c>
-      <c r="F8" s="71">
+      <c r="F8" s="70">
         <v>139402</v>
       </c>
-      <c r="G8" s="71">
+      <c r="G8" s="70">
         <v>141446</v>
       </c>
-      <c r="H8" s="72">
+      <c r="H8" s="71">
         <v>141816</v>
       </c>
       <c r="I8" s="8"/>
@@ -9702,22 +9709,22 @@
       <c r="A9" s="11">
         <v>2002</v>
       </c>
-      <c r="B9" s="70">
+      <c r="B9" s="69">
         <v>82295</v>
       </c>
-      <c r="C9" s="71">
+      <c r="C9" s="70">
         <v>126112</v>
       </c>
-      <c r="D9" s="71">
+      <c r="D9" s="70">
         <v>139094</v>
       </c>
-      <c r="E9" s="71">
+      <c r="E9" s="70">
         <v>146112</v>
       </c>
-      <c r="F9" s="71">
+      <c r="F9" s="70">
         <v>149292</v>
       </c>
-      <c r="G9" s="72">
+      <c r="G9" s="71">
         <v>150819</v>
       </c>
       <c r="H9" s="8"/>
@@ -9729,19 +9736,19 @@
       <c r="A10" s="11">
         <v>2003</v>
       </c>
-      <c r="B10" s="70">
+      <c r="B10" s="69">
         <v>81672</v>
       </c>
-      <c r="C10" s="71">
+      <c r="C10" s="70">
         <v>129999</v>
       </c>
-      <c r="D10" s="71">
+      <c r="D10" s="70">
         <v>143206</v>
       </c>
-      <c r="E10" s="71">
+      <c r="E10" s="70">
         <v>151112</v>
       </c>
-      <c r="F10" s="72">
+      <c r="F10" s="71">
         <v>154348</v>
       </c>
       <c r="G10" s="8"/>
@@ -9754,16 +9761,16 @@
       <c r="A11" s="11">
         <v>2004</v>
       </c>
-      <c r="B11" s="70">
+      <c r="B11" s="69">
         <v>97575</v>
       </c>
-      <c r="C11" s="71">
+      <c r="C11" s="70">
         <v>146722</v>
       </c>
-      <c r="D11" s="71">
+      <c r="D11" s="70">
         <v>161677</v>
       </c>
-      <c r="E11" s="72">
+      <c r="E11" s="71">
         <v>170055</v>
       </c>
       <c r="F11" s="8"/>
@@ -9777,13 +9784,13 @@
       <c r="A12" s="11">
         <v>2005</v>
       </c>
-      <c r="B12" s="70">
+      <c r="B12" s="69">
         <v>98552</v>
       </c>
-      <c r="C12" s="71">
+      <c r="C12" s="70">
         <v>152039</v>
       </c>
-      <c r="D12" s="72">
+      <c r="D12" s="71">
         <v>165521</v>
       </c>
       <c r="E12" s="8"/>
@@ -9798,10 +9805,10 @@
       <c r="A13" s="11">
         <v>2006</v>
       </c>
-      <c r="B13" s="70">
+      <c r="B13" s="69">
         <v>86424</v>
       </c>
-      <c r="C13" s="72">
+      <c r="C13" s="71">
         <v>140342</v>
       </c>
       <c r="D13" s="8"/>
@@ -9817,7 +9824,7 @@
       <c r="A14" s="9">
         <v>2007</v>
       </c>
-      <c r="B14" s="72">
+      <c r="B14" s="71">
         <v>106588</v>
       </c>
       <c r="C14" s="8"/>
@@ -9850,7 +9857,7 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -9859,25 +9866,25 @@
       <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="27" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10385,7 +10392,7 @@
       <c r="J18" s="2">
         <v>9</v>
       </c>
-      <c r="K18" s="26">
+      <c r="K18" s="25">
         <v>10</v>
       </c>
     </row>
@@ -10501,7 +10508,7 @@
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>51</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -10521,11 +10528,11 @@
       <c r="A2" s="2">
         <v>1998</v>
       </c>
-      <c r="B2" s="35" cm="1">
+      <c r="B2" s="34" cm="1">
         <f t="array" ref="B2">_xlfn.XLOOKUP(TRUE, Triangle!B5:K5&lt;&gt;"",Triangle!B5:K5, ,0,-1)</f>
         <v>126038</v>
       </c>
-      <c r="C2" s="33" cm="1">
+      <c r="C2" s="32" cm="1">
         <f t="array" ref="C2">_xlfn.XLOOKUP(TRUE, Triangle!B5:K5&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>10</v>
       </c>
@@ -10533,11 +10540,11 @@
         <f>_xlfn.XLOOKUP(C2,Factors!$B$18:$K$18,Factors!$B$19:$K$19, ,0,1)</f>
         <v>1</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="33">
         <f>B2*D2</f>
         <v>126038</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="33">
         <f>E2-B2</f>
         <v>0</v>
       </c>
@@ -10546,11 +10553,11 @@
       <c r="A3" s="2">
         <v>1999</v>
       </c>
-      <c r="B3" s="36" cm="1">
+      <c r="B3" s="35" cm="1">
         <f t="array" ref="B3">_xlfn.XLOOKUP(TRUE, Triangle!B6:K6&lt;&gt;"",Triangle!B6:K6, ,0,-1)</f>
         <v>137247</v>
       </c>
-      <c r="C3" s="30" cm="1">
+      <c r="C3" s="29" cm="1">
         <f t="array" ref="C3">_xlfn.XLOOKUP(TRUE, Triangle!B6:K6&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>9</v>
       </c>
@@ -10558,11 +10565,11 @@
         <f>_xlfn.XLOOKUP(C3,Factors!$B$18:$K$18,Factors!$B$19:$K$19, ,0,1)</f>
         <v>1.00083377669078</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="30">
         <f t="shared" ref="E3:E11" si="0">B3*D3</f>
         <v>137361.43334947948</v>
       </c>
-      <c r="F3" s="31">
+      <c r="F3" s="30">
         <f t="shared" ref="F3:F11" si="1">E3-B3</f>
         <v>114.4333494794846</v>
       </c>
@@ -10571,11 +10578,11 @@
       <c r="A4" s="2">
         <v>2000</v>
       </c>
-      <c r="B4" s="36" cm="1">
+      <c r="B4" s="35" cm="1">
         <f t="array" ref="B4">_xlfn.XLOOKUP(TRUE, Triangle!B7:K7&lt;&gt;"",Triangle!B7:K7, ,0,-1)</f>
         <v>141264</v>
       </c>
-      <c r="C4" s="30" cm="1">
+      <c r="C4" s="29" cm="1">
         <f t="array" ref="C4">_xlfn.XLOOKUP(TRUE, Triangle!B7:K7&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>8</v>
       </c>
@@ -10583,11 +10590,11 @@
         <f>_xlfn.XLOOKUP(C4,Factors!$B$18:$K$18,Factors!$B$19:$K$19, ,0,1)</f>
         <v>1.001892086593025</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="30">
         <f t="shared" si="0"/>
         <v>141531.28372047708</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="30">
         <f t="shared" si="1"/>
         <v>267.28372047707671</v>
       </c>
@@ -10596,11 +10603,11 @@
       <c r="A5" s="2">
         <v>2001</v>
       </c>
-      <c r="B5" s="36" cm="1">
+      <c r="B5" s="35" cm="1">
         <f t="array" ref="B5">_xlfn.XLOOKUP(TRUE, Triangle!B8:K8&lt;&gt;"",Triangle!B8:K8, ,0,-1)</f>
         <v>141816</v>
       </c>
-      <c r="C5" s="30" cm="1">
+      <c r="C5" s="29" cm="1">
         <f t="array" ref="C5">_xlfn.XLOOKUP(TRUE, Triangle!B8:K8&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>7</v>
       </c>
@@ -10608,11 +10615,11 @@
         <f>_xlfn.XLOOKUP(C5,Factors!$B$18:$K$18,Factors!$B$19:$K$19, ,0,1)</f>
         <v>1.0045391032767386</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <f t="shared" si="0"/>
         <v>142459.71747029395</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <f t="shared" si="1"/>
         <v>643.71747029395192</v>
       </c>
@@ -10621,11 +10628,11 @@
       <c r="A6" s="2">
         <v>2002</v>
       </c>
-      <c r="B6" s="36" cm="1">
+      <c r="B6" s="35" cm="1">
         <f t="array" ref="B6">_xlfn.XLOOKUP(TRUE, Triangle!B9:K9&lt;&gt;"",Triangle!B9:K9, ,0,-1)</f>
         <v>150819</v>
       </c>
-      <c r="C6" s="30" cm="1">
+      <c r="C6" s="29" cm="1">
         <f t="array" ref="C6">_xlfn.XLOOKUP(TRUE, Triangle!B9:K9&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>6</v>
       </c>
@@ -10633,11 +10640,11 @@
         <f>_xlfn.XLOOKUP(C6,Factors!$B$18:$K$18,Factors!$B$19:$K$19, ,0,1)</f>
         <v>1.0080094035998213</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <f t="shared" si="0"/>
         <v>152026.97024152146</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <f t="shared" si="1"/>
         <v>1207.970241521456</v>
       </c>
@@ -10646,11 +10653,11 @@
       <c r="A7" s="2">
         <v>2003</v>
       </c>
-      <c r="B7" s="36" cm="1">
+      <c r="B7" s="35" cm="1">
         <f t="array" ref="B7">_xlfn.XLOOKUP(TRUE, Triangle!B10:K10&lt;&gt;"",Triangle!B10:K10, ,0,-1)</f>
         <v>154348</v>
       </c>
-      <c r="C7" s="30" cm="1">
+      <c r="C7" s="29" cm="1">
         <f t="array" ref="C7">_xlfn.XLOOKUP(TRUE, Triangle!B10:K10&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>5</v>
       </c>
@@ -10658,11 +10665,11 @@
         <f>_xlfn.XLOOKUP(C7,Factors!$B$18:$K$18,Factors!$B$19:$K$19, ,0,1)</f>
         <v>1.0184098477545336</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <f t="shared" si="0"/>
         <v>157189.52318121676</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <f t="shared" si="1"/>
         <v>2841.5231812167622</v>
       </c>
@@ -10671,11 +10678,11 @@
       <c r="A8" s="2">
         <v>2004</v>
       </c>
-      <c r="B8" s="36" cm="1">
+      <c r="B8" s="35" cm="1">
         <f t="array" ref="B8">_xlfn.XLOOKUP(TRUE, Triangle!B11:K11&lt;&gt;"",Triangle!B11:K11, ,0,-1)</f>
         <v>170055</v>
       </c>
-      <c r="C8" s="30" cm="1">
+      <c r="C8" s="29" cm="1">
         <f t="array" ref="C8">_xlfn.XLOOKUP(TRUE, Triangle!B11:K11&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>4</v>
       </c>
@@ -10683,11 +10690,11 @@
         <f>_xlfn.XLOOKUP(C8,Factors!$B$18:$K$18,Factors!$B$19:$K$19, ,0,1)</f>
         <v>1.0381189039644634</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <f t="shared" si="0"/>
         <v>176537.31021367683</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <f t="shared" si="1"/>
         <v>6482.3102136768284</v>
       </c>
@@ -10696,11 +10703,11 @@
       <c r="A9" s="2">
         <v>2005</v>
       </c>
-      <c r="B9" s="36" cm="1">
+      <c r="B9" s="35" cm="1">
         <f t="array" ref="B9">_xlfn.XLOOKUP(TRUE, Triangle!B12:K12&lt;&gt;"",Triangle!B12:K12, ,0,-1)</f>
         <v>165521</v>
       </c>
-      <c r="C9" s="30" cm="1">
+      <c r="C9" s="29" cm="1">
         <f t="array" ref="C9">_xlfn.XLOOKUP(TRUE, Triangle!B12:K12&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>3</v>
       </c>
@@ -10708,11 +10715,11 @@
         <f>_xlfn.XLOOKUP(C9,Factors!$B$18:$K$18,Factors!$B$19:$K$19, ,0,1)</f>
         <v>1.0906602040365321</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <f t="shared" si="0"/>
         <v>180527.16763233082</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <f t="shared" si="1"/>
         <v>15006.16763233082</v>
       </c>
@@ -10721,11 +10728,11 @@
       <c r="A10" s="2">
         <v>2006</v>
       </c>
-      <c r="B10" s="36" cm="1">
+      <c r="B10" s="35" cm="1">
         <f t="array" ref="B10">_xlfn.XLOOKUP(TRUE, Triangle!B13:K13&lt;&gt;"",Triangle!B13:K13, ,0,-1)</f>
         <v>140342</v>
       </c>
-      <c r="C10" s="30" cm="1">
+      <c r="C10" s="29" cm="1">
         <f t="array" ref="C10">_xlfn.XLOOKUP(TRUE, Triangle!B13:K13&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>2</v>
       </c>
@@ -10733,11 +10740,11 @@
         <f>_xlfn.XLOOKUP(C10,Factors!$B$18:$K$18,Factors!$B$19:$K$19, ,0,1)</f>
         <v>1.1992148705445815</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <f t="shared" si="0"/>
         <v>168300.21336196768</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <f t="shared" si="1"/>
         <v>27958.213361967675</v>
       </c>
@@ -10746,11 +10753,11 @@
       <c r="A11" s="2">
         <v>2007</v>
       </c>
-      <c r="B11" s="39" cm="1">
+      <c r="B11" s="37" cm="1">
         <f t="array" ref="B11">_xlfn.XLOOKUP(TRUE, Triangle!B14:K14&lt;&gt;"",Triangle!B14:K14, ,0,-1)</f>
         <v>106588</v>
       </c>
-      <c r="C11" s="40" cm="1">
+      <c r="C11" s="38" cm="1">
         <f t="array" ref="C11">_xlfn.XLOOKUP(TRUE, Triangle!B14:K14&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>1</v>
       </c>
@@ -10758,30 +10765,30 @@
         <f>_xlfn.XLOOKUP(C11,Factors!$B$18:$K$18,Factors!$B$19:$K$19, ,0,1)</f>
         <v>1.8591654828090445</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="39">
         <f t="shared" si="0"/>
         <v>198164.73048165042</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="39">
         <f t="shared" si="1"/>
         <v>91576.730481650418</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="41">
         <f>SUM(B2:B11)</f>
         <v>1434038</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="45">
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="43">
         <f>SUM(E2:E11)</f>
         <v>1580136.3496526144</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="43">
         <f>SUM(F2:F11)</f>
         <v>146098.34965261447</v>
       </c>
@@ -10811,7 +10818,7 @@
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>48</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -10840,15 +10847,15 @@
       <c r="A2" s="2">
         <v>1998</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="34">
         <f>_xlfn.XLOOKUP(A2,Table1[AccidentYear],Table1[EarnedPremDIR (in thousands)], ,0,1)</f>
         <v>177563</v>
       </c>
-      <c r="C2" s="47" cm="1">
+      <c r="C2" s="45" cm="1">
         <f t="array" ref="C2">AVERAGE('Chain Ladder'!$E$2:$E$5/BF!$B$2:$B$5)</f>
         <v>0.74662324237202315</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="33">
         <f>B2*C2</f>
         <v>132572.66278530355</v>
       </c>
@@ -10856,19 +10863,19 @@
         <f>_xlfn.XLOOKUP(A2,'Chain Ladder'!A2:A11,'Chain Ladder'!D2:D11,,0,1)</f>
         <v>1</v>
       </c>
-      <c r="F2" s="49">
+      <c r="F2" s="47">
         <f>1-(1/E2)</f>
         <v>0</v>
       </c>
-      <c r="G2" s="32" cm="1">
+      <c r="G2" s="31" cm="1">
         <f t="array" ref="G2">_xlfn.XLOOKUP(TRUE,Triangle!B5:K5&lt;&gt;"",Triangle!B5:K5,,0,-1)</f>
         <v>126038</v>
       </c>
-      <c r="H2" s="34">
+      <c r="H2" s="33">
         <f>G2+(D2*F2)</f>
         <v>126038</v>
       </c>
-      <c r="I2" s="34">
+      <c r="I2" s="33">
         <f>H2-G2</f>
         <v>0</v>
       </c>
@@ -10877,15 +10884,15 @@
       <c r="A3" s="2">
         <v>1999</v>
       </c>
-      <c r="B3" s="36">
+      <c r="B3" s="35">
         <f>_xlfn.XLOOKUP(A3,Table1[AccidentYear],Table1[EarnedPremDIR (in thousands)], ,0,1)</f>
         <v>180249</v>
       </c>
-      <c r="C3" s="48" cm="1">
+      <c r="C3" s="46" cm="1">
         <f t="array" ref="C3">AVERAGE('Chain Ladder'!$E$2:$E$5/BF!$B$2:$B$5)</f>
         <v>0.74662324237202315</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="30">
         <f t="shared" ref="D3:D11" si="0">B3*C3</f>
         <v>134578.09281431479</v>
       </c>
@@ -10893,19 +10900,19 @@
         <f>_xlfn.XLOOKUP(A3,'Chain Ladder'!A3:A12,'Chain Ladder'!D3:D12,,0,1)</f>
         <v>1.00083377669078</v>
       </c>
-      <c r="F3" s="50">
+      <c r="F3" s="48">
         <f t="shared" ref="F3:F11" si="1">1-(1/E3)</f>
         <v>8.3308208635490821E-4</v>
       </c>
-      <c r="G3" s="29" cm="1">
+      <c r="G3" s="28" cm="1">
         <f t="array" ref="G3">_xlfn.XLOOKUP(TRUE,Triangle!B6:K6&lt;&gt;"",Triangle!B6:K6,,0,-1)</f>
         <v>137247</v>
       </c>
-      <c r="H3" s="31">
+      <c r="H3" s="30">
         <f t="shared" ref="H3:H11" si="2">G3+(D3*F3)</f>
         <v>137359.11459833942</v>
       </c>
-      <c r="I3" s="31">
+      <c r="I3" s="30">
         <f t="shared" ref="I3:I11" si="3">H3-G3</f>
         <v>112.11459833942354</v>
       </c>
@@ -10914,15 +10921,15 @@
       <c r="A4" s="2">
         <v>2000</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="35">
         <f>_xlfn.XLOOKUP(A4,Table1[AccidentYear],Table1[EarnedPremDIR (in thousands)], ,0,1)</f>
         <v>183981</v>
       </c>
-      <c r="C4" s="48" cm="1">
+      <c r="C4" s="46" cm="1">
         <f t="array" ref="C4">AVERAGE('Chain Ladder'!$E$2:$E$5/BF!$B$2:$B$5)</f>
         <v>0.74662324237202315</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="30">
         <f t="shared" si="0"/>
         <v>137364.49075484718</v>
       </c>
@@ -10930,19 +10937,19 @@
         <f>_xlfn.XLOOKUP(A4,'Chain Ladder'!A4:A13,'Chain Ladder'!D4:D13,,0,1)</f>
         <v>1.001892086593025</v>
       </c>
-      <c r="F4" s="50">
+      <c r="F4" s="48">
         <f t="shared" si="1"/>
         <v>1.8885133622116301E-3</v>
       </c>
-      <c r="G4" s="29" cm="1">
+      <c r="G4" s="28" cm="1">
         <f t="array" ref="G4">_xlfn.XLOOKUP(TRUE,Triangle!B7:K7&lt;&gt;"",Triangle!B7:K7,,0,-1)</f>
         <v>141264</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="30">
         <f t="shared" si="2"/>
         <v>141523.41467628392</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="30">
         <f t="shared" si="3"/>
         <v>259.41467628392274</v>
       </c>
@@ -10951,15 +10958,15 @@
       <c r="A5" s="2">
         <v>2001</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="35">
         <f>_xlfn.XLOOKUP(A5,Table1[AccidentYear],Table1[EarnedPremDIR (in thousands)], ,0,1)</f>
         <v>191135</v>
       </c>
-      <c r="C5" s="48" cm="1">
+      <c r="C5" s="46" cm="1">
         <f t="array" ref="C5">AVERAGE('Chain Ladder'!$E$2:$E$5/BF!$B$2:$B$5)</f>
         <v>0.74662324237202315</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <f t="shared" si="0"/>
         <v>142705.83343077663</v>
       </c>
@@ -10967,19 +10974,19 @@
         <f>_xlfn.XLOOKUP(A5,'Chain Ladder'!A5:A14,'Chain Ladder'!D5:D14,,0,1)</f>
         <v>1.0045391032767386</v>
       </c>
-      <c r="F5" s="50">
+      <c r="F5" s="48">
         <f t="shared" si="1"/>
         <v>4.5185929168235495E-3</v>
       </c>
-      <c r="G5" s="29" cm="1">
+      <c r="G5" s="28" cm="1">
         <f t="array" ref="G5">_xlfn.XLOOKUP(TRUE,Triangle!B8:K8&lt;&gt;"",Triangle!B8:K8,,0,-1)</f>
         <v>141816</v>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="30">
         <f t="shared" si="2"/>
         <v>142460.8295681297</v>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="30">
         <f t="shared" si="3"/>
         <v>644.82956812970224</v>
       </c>
@@ -10988,15 +10995,15 @@
       <c r="A6" s="2">
         <v>2002</v>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="35">
         <f>_xlfn.XLOOKUP(A6,Table1[AccidentYear],Table1[EarnedPremDIR (in thousands)], ,0,1)</f>
         <v>207149</v>
       </c>
-      <c r="C6" s="48" cm="1">
+      <c r="C6" s="46" cm="1">
         <f t="array" ref="C6">AVERAGE('Chain Ladder'!$E$2:$E$5/BF!$B$2:$B$5)</f>
         <v>0.74662324237202315</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <f t="shared" si="0"/>
         <v>154662.25803412223</v>
       </c>
@@ -11004,19 +11011,19 @@
         <f>_xlfn.XLOOKUP(A6,'Chain Ladder'!A6:A15,'Chain Ladder'!D6:D15,,0,1)</f>
         <v>1.0080094035998213</v>
       </c>
-      <c r="F6" s="50">
+      <c r="F6" s="48">
         <f t="shared" si="1"/>
         <v>7.9457627788173113E-3</v>
       </c>
-      <c r="G6" s="29" cm="1">
+      <c r="G6" s="28" cm="1">
         <f t="array" ref="G6">_xlfn.XLOOKUP(TRUE,Triangle!B9:K9&lt;&gt;"",Triangle!B9:K9,,0,-1)</f>
         <v>150819</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="30">
         <f t="shared" si="2"/>
         <v>152047.90961317538</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="30">
         <f t="shared" si="3"/>
         <v>1228.9096131753759</v>
       </c>
@@ -11025,15 +11032,15 @@
       <c r="A7" s="2">
         <v>2003</v>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="35">
         <f>_xlfn.XLOOKUP(A7,Table1[AccidentYear],Table1[EarnedPremDIR (in thousands)], ,0,1)</f>
         <v>214963</v>
       </c>
-      <c r="C7" s="48" cm="1">
+      <c r="C7" s="46" cm="1">
         <f t="array" ref="C7">AVERAGE('Chain Ladder'!$E$2:$E$5/BF!$B$2:$B$5)</f>
         <v>0.74662324237202315</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <f t="shared" si="0"/>
         <v>160496.37205001721</v>
       </c>
@@ -11041,19 +11048,19 @@
         <f>_xlfn.XLOOKUP(A7,'Chain Ladder'!A7:A16,'Chain Ladder'!D7:D16,,0,1)</f>
         <v>1.0184098477545336</v>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="48">
         <f t="shared" si="1"/>
         <v>1.8077051979735859E-2</v>
       </c>
-      <c r="G7" s="29" cm="1">
+      <c r="G7" s="28" cm="1">
         <f t="array" ref="G7">_xlfn.XLOOKUP(TRUE,Triangle!B10:K10&lt;&gt;"",Triangle!B10:K10,,0,-1)</f>
         <v>154348</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="30">
         <f t="shared" si="2"/>
         <v>157249.3012601072</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="30">
         <f t="shared" si="3"/>
         <v>2901.3012601071969</v>
       </c>
@@ -11062,15 +11069,15 @@
       <c r="A8" s="2">
         <v>2004</v>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="35">
         <f>_xlfn.XLOOKUP(A8,Table1[AccidentYear],Table1[EarnedPremDIR (in thousands)], ,0,1)</f>
         <v>224282</v>
       </c>
-      <c r="C8" s="48" cm="1">
+      <c r="C8" s="46" cm="1">
         <f t="array" ref="C8">AVERAGE('Chain Ladder'!$E$2:$E$5/BF!$B$2:$B$5)</f>
         <v>0.74662324237202315</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <f t="shared" si="0"/>
         <v>167454.15404568211</v>
       </c>
@@ -11078,19 +11085,19 @@
         <f>_xlfn.XLOOKUP(A8,'Chain Ladder'!A8:A17,'Chain Ladder'!D8:D17,,0,1)</f>
         <v>1.0381189039644634</v>
       </c>
-      <c r="F8" s="50">
+      <c r="F8" s="48">
         <f t="shared" si="1"/>
         <v>3.6719208001021242E-2</v>
       </c>
-      <c r="G8" s="29" cm="1">
+      <c r="G8" s="28" cm="1">
         <f t="array" ref="G8">_xlfn.XLOOKUP(TRUE,Triangle!B11:K11&lt;&gt;"",Triangle!B11:K11,,0,-1)</f>
         <v>170055</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="30">
         <f t="shared" si="2"/>
         <v>176203.78391303847</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="30">
         <f t="shared" si="3"/>
         <v>6148.7839130384673</v>
       </c>
@@ -11099,15 +11106,15 @@
       <c r="A9" s="2">
         <v>2005</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="35">
         <f>_xlfn.XLOOKUP(A9,Table1[AccidentYear],Table1[EarnedPremDIR (in thousands)], ,0,1)</f>
         <v>236170</v>
       </c>
-      <c r="C9" s="48" cm="1">
+      <c r="C9" s="46" cm="1">
         <f t="array" ref="C9">AVERAGE('Chain Ladder'!$E$2:$E$5/BF!$B$2:$B$5)</f>
         <v>0.74662324237202315</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <f t="shared" si="0"/>
         <v>176330.01115100071</v>
       </c>
@@ -11115,19 +11122,19 @@
         <f>_xlfn.XLOOKUP(A9,'Chain Ladder'!A9:A18,'Chain Ladder'!D9:D18,,0,1)</f>
         <v>1.0906602040365321</v>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="48">
         <f t="shared" si="1"/>
         <v>8.3124151501080545E-2</v>
       </c>
-      <c r="G9" s="29" cm="1">
+      <c r="G9" s="28" cm="1">
         <f t="array" ref="G9">_xlfn.XLOOKUP(TRUE,Triangle!B12:K12&lt;&gt;"",Triangle!B12:K12,,0,-1)</f>
         <v>165521</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="30">
         <f t="shared" si="2"/>
         <v>180178.282561103</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="30">
         <f t="shared" si="3"/>
         <v>14657.282561102998</v>
       </c>
@@ -11136,15 +11143,15 @@
       <c r="A10" s="2">
         <v>2006</v>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="35">
         <f>_xlfn.XLOOKUP(A10,Table1[AccidentYear],Table1[EarnedPremDIR (in thousands)], ,0,1)</f>
         <v>248235</v>
       </c>
-      <c r="C10" s="48" cm="1">
+      <c r="C10" s="46" cm="1">
         <f t="array" ref="C10">AVERAGE('Chain Ladder'!$E$2:$E$5/BF!$B$2:$B$5)</f>
         <v>0.74662324237202315</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <f t="shared" si="0"/>
         <v>185338.02057021917</v>
       </c>
@@ -11152,19 +11159,19 @@
         <f>_xlfn.XLOOKUP(A10,'Chain Ladder'!A10:A19,'Chain Ladder'!D10:D19,,0,1)</f>
         <v>1.1992148705445815</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="48">
         <f t="shared" si="1"/>
         <v>0.16612108091531175</v>
       </c>
-      <c r="G10" s="29" cm="1">
+      <c r="G10" s="28" cm="1">
         <f t="array" ref="G10">_xlfn.XLOOKUP(TRUE,Triangle!B13:K13&lt;&gt;"",Triangle!B13:K13,,0,-1)</f>
         <v>140342</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="30">
         <f t="shared" si="2"/>
         <v>171130.55231182909</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="30">
         <f t="shared" si="3"/>
         <v>30788.552311829088</v>
       </c>
@@ -11173,41 +11180,72 @@
       <c r="A11" s="2">
         <v>2007</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>_xlfn.XLOOKUP(A11,Table1[AccidentYear],Table1[EarnedPremDIR (in thousands)], ,0,1)</f>
         <v>253531</v>
       </c>
-      <c r="C11" s="48" cm="1">
+      <c r="C11" s="73" cm="1">
         <f t="array" ref="C11">AVERAGE('Chain Ladder'!$E$2:$E$5/BF!$B$2:$B$5)</f>
         <v>0.74662324237202315</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="39">
         <f t="shared" si="0"/>
         <v>189292.13726182139</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="16">
         <f>_xlfn.XLOOKUP(A11,'Chain Ladder'!A11:A20,'Chain Ladder'!D11:D20,,0,1)</f>
         <v>1.8591654828090445</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="74">
         <f t="shared" si="1"/>
         <v>0.46212426529720041</v>
       </c>
-      <c r="G11" s="29" cm="1">
+      <c r="G11" s="75" cm="1">
         <f t="array" ref="G11">_xlfn.XLOOKUP(TRUE,Triangle!B14:K14&lt;&gt;"",Triangle!B14:K14,,0,-1)</f>
         <v>106588</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="39">
         <f t="shared" si="2"/>
         <v>194064.48985865602</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="39">
         <f t="shared" si="3"/>
         <v>87476.489858656016</v>
       </c>
     </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="77">
+        <f>SUM(B2:B11)</f>
+        <v>2117258</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="D12" s="78">
+        <f>SUM(D2:D11)</f>
+        <v>1580794.032898105</v>
+      </c>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="78">
+        <f>SUM(G2:G11)</f>
+        <v>1434038</v>
+      </c>
+      <c r="H12" s="78">
+        <f>SUM(H2:H11)</f>
+        <v>1578255.678360662</v>
+      </c>
+      <c r="I12" s="78">
+        <f>SUM(I2:I11)</f>
+        <v>144217.67836066219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G15" s="44"/>
+    </row>
     <row r="19" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="46"/>
+      <c r="E19" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11216,7 +11254,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A05CCE6C-190C-4D45-9D43-8E0674EBA66A}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -11255,27 +11293,27 @@
       <c r="A2" s="2">
         <v>1998</v>
       </c>
-      <c r="B2" s="57">
+      <c r="B2" s="55">
         <f>'Chain Ladder'!E2</f>
         <v>126038</v>
       </c>
-      <c r="C2" s="58">
+      <c r="C2" s="56">
         <f>'Chain Ladder'!F2</f>
         <v>0</v>
       </c>
-      <c r="D2" s="58">
+      <c r="D2" s="56">
         <f>BF!H2</f>
         <v>126038</v>
       </c>
-      <c r="E2" s="58">
+      <c r="E2" s="56">
         <f>BF!I2</f>
         <v>0</v>
       </c>
-      <c r="F2" s="59">
+      <c r="F2" s="57">
         <f>E2-C2</f>
         <v>0</v>
       </c>
-      <c r="G2" s="52">
+      <c r="G2" s="50">
         <f>IFERROR(F2/C2,0)</f>
         <v>0</v>
       </c>
@@ -11284,27 +11322,27 @@
       <c r="A3" s="2">
         <v>1999</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="58">
         <f>'Chain Ladder'!E3</f>
         <v>137361.43334947948</v>
       </c>
-      <c r="C3" s="61">
+      <c r="C3" s="59">
         <f>'Chain Ladder'!F3</f>
         <v>114.4333494794846</v>
       </c>
-      <c r="D3" s="61">
+      <c r="D3" s="59">
         <f>BF!H3</f>
         <v>137359.11459833942</v>
       </c>
-      <c r="E3" s="61">
+      <c r="E3" s="59">
         <f>BF!I3</f>
         <v>112.11459833942354</v>
       </c>
-      <c r="F3" s="62">
+      <c r="F3" s="60">
         <f t="shared" ref="F3:F11" si="0">E3-C3</f>
         <v>-2.3187511400610674</v>
       </c>
-      <c r="G3" s="51">
+      <c r="G3" s="49">
         <f t="shared" ref="G3:G11" si="1">IFERROR(F3/C3,0)</f>
         <v>-2.0262896704572726E-2</v>
       </c>
@@ -11313,27 +11351,27 @@
       <c r="A4" s="2">
         <v>2000</v>
       </c>
-      <c r="B4" s="60">
+      <c r="B4" s="58">
         <f>'Chain Ladder'!E4</f>
         <v>141531.28372047708</v>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="59">
         <f>'Chain Ladder'!F4</f>
         <v>267.28372047707671</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="59">
         <f>BF!H4</f>
         <v>141523.41467628392</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="59">
         <f>BF!I4</f>
         <v>259.41467628392274</v>
       </c>
-      <c r="F4" s="62">
+      <c r="F4" s="60">
         <f t="shared" si="0"/>
         <v>-7.8690441931539681</v>
       </c>
-      <c r="G4" s="51">
+      <c r="G4" s="49">
         <f t="shared" si="1"/>
         <v>-2.9440791152968285E-2</v>
       </c>
@@ -11342,27 +11380,27 @@
       <c r="A5" s="2">
         <v>2001</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="58">
         <f>'Chain Ladder'!E5</f>
         <v>142459.71747029395</v>
       </c>
-      <c r="C5" s="61">
+      <c r="C5" s="59">
         <f>'Chain Ladder'!F5</f>
         <v>643.71747029395192</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="59">
         <f>BF!H5</f>
         <v>142460.8295681297</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="59">
         <f>BF!I5</f>
         <v>644.82956812970224</v>
       </c>
-      <c r="F5" s="62">
+      <c r="F5" s="60">
         <f t="shared" si="0"/>
         <v>1.1120978357503191</v>
       </c>
-      <c r="G5" s="51">
+      <c r="G5" s="49">
         <f t="shared" si="1"/>
         <v>1.7276179179081196E-3</v>
       </c>
@@ -11371,27 +11409,27 @@
       <c r="A6" s="2">
         <v>2002</v>
       </c>
-      <c r="B6" s="60">
+      <c r="B6" s="58">
         <f>'Chain Ladder'!E6</f>
         <v>152026.97024152146</v>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="59">
         <f>'Chain Ladder'!F6</f>
         <v>1207.970241521456</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="59">
         <f>BF!H6</f>
         <v>152047.90961317538</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="59">
         <f>BF!I6</f>
         <v>1228.9096131753759</v>
       </c>
-      <c r="F6" s="62">
+      <c r="F6" s="60">
         <f t="shared" si="0"/>
         <v>20.939371653919807</v>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="49">
         <f t="shared" si="1"/>
         <v>1.7334343954985485E-2</v>
       </c>
@@ -11400,27 +11438,27 @@
       <c r="A7" s="2">
         <v>2003</v>
       </c>
-      <c r="B7" s="60">
+      <c r="B7" s="58">
         <f>'Chain Ladder'!E7</f>
         <v>157189.52318121676</v>
       </c>
-      <c r="C7" s="61">
+      <c r="C7" s="59">
         <f>'Chain Ladder'!F7</f>
         <v>2841.5231812167622</v>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="59">
         <f>BF!H7</f>
         <v>157249.3012601072</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="59">
         <f>BF!I7</f>
         <v>2901.3012601071969</v>
       </c>
-      <c r="F7" s="62">
+      <c r="F7" s="60">
         <f t="shared" si="0"/>
         <v>59.778078890434699</v>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="49">
         <f t="shared" si="1"/>
         <v>2.1037336343262651E-2</v>
       </c>
@@ -11429,27 +11467,27 @@
       <c r="A8" s="2">
         <v>2004</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="58">
         <f>'Chain Ladder'!E8</f>
         <v>176537.31021367683</v>
       </c>
-      <c r="C8" s="61">
+      <c r="C8" s="59">
         <f>'Chain Ladder'!F8</f>
         <v>6482.3102136768284</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="59">
         <f>BF!H8</f>
         <v>176203.78391303847</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="59">
         <f>BF!I8</f>
         <v>6148.7839130384673</v>
       </c>
-      <c r="F8" s="62">
+      <c r="F8" s="60">
         <f t="shared" si="0"/>
         <v>-333.52630063836114</v>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="49">
         <f t="shared" si="1"/>
         <v>-5.1451764825241497E-2</v>
       </c>
@@ -11458,27 +11496,27 @@
       <c r="A9" s="2">
         <v>2005</v>
       </c>
-      <c r="B9" s="60">
+      <c r="B9" s="58">
         <f>'Chain Ladder'!E9</f>
         <v>180527.16763233082</v>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="59">
         <f>'Chain Ladder'!F9</f>
         <v>15006.16763233082</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="59">
         <f>BF!H9</f>
         <v>180178.282561103</v>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="59">
         <f>BF!I9</f>
         <v>14657.282561102998</v>
       </c>
-      <c r="F9" s="62">
+      <c r="F9" s="60">
         <f t="shared" si="0"/>
         <v>-348.88507122782175</v>
       </c>
-      <c r="G9" s="51">
+      <c r="G9" s="49">
         <f t="shared" si="1"/>
         <v>-2.3249445146550817E-2</v>
       </c>
@@ -11487,27 +11525,27 @@
       <c r="A10" s="2">
         <v>2006</v>
       </c>
-      <c r="B10" s="60">
+      <c r="B10" s="58">
         <f>'Chain Ladder'!E10</f>
         <v>168300.21336196768</v>
       </c>
-      <c r="C10" s="61">
+      <c r="C10" s="59">
         <f>'Chain Ladder'!F10</f>
         <v>27958.213361967675</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="59">
         <f>BF!H10</f>
         <v>171130.55231182909</v>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="59">
         <f>BF!I10</f>
         <v>30788.552311829088</v>
       </c>
-      <c r="F10" s="62">
+      <c r="F10" s="60">
         <f t="shared" si="0"/>
         <v>2830.3389498614124</v>
       </c>
-      <c r="G10" s="51">
+      <c r="G10" s="49">
         <f t="shared" si="1"/>
         <v>0.10123461443039132</v>
       </c>
@@ -11516,60 +11554,64 @@
       <c r="A11" s="2">
         <v>2007</v>
       </c>
-      <c r="B11" s="63">
+      <c r="B11" s="61">
         <f>'Chain Ladder'!E11</f>
         <v>198164.73048165042</v>
       </c>
-      <c r="C11" s="64">
+      <c r="C11" s="62">
         <f>'Chain Ladder'!F11</f>
         <v>91576.730481650418</v>
       </c>
-      <c r="D11" s="64">
+      <c r="D11" s="62">
         <f>BF!H11</f>
         <v>194064.48985865602</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="62">
         <f>BF!I11</f>
         <v>87476.489858656016</v>
       </c>
-      <c r="F11" s="65">
+      <c r="F11" s="63">
         <f t="shared" si="0"/>
         <v>-4100.2406229944027</v>
       </c>
-      <c r="G11" s="53">
+      <c r="G11" s="51">
         <f t="shared" si="1"/>
         <v>-4.4773826292214963E-2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="67">
+      <c r="B12" s="54"/>
+      <c r="C12" s="65">
         <f>SUM(C2:C11)</f>
         <v>146098.34965261447</v>
       </c>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67">
+      <c r="D12" s="65"/>
+      <c r="E12" s="65">
         <f>SUM(E2:E11)</f>
         <v>144217.67836066219</v>
       </c>
-      <c r="F12" s="55"/>
-      <c r="G12" s="66">
+      <c r="F12" s="53"/>
+      <c r="G12" s="64">
         <f>(E12-C12)/C12</f>
         <v>-1.2872638852006554E-2</v>
       </c>
     </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F23" s="67"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup scale="37" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10816AD4-4FDD-4ADA-AFD0-90A8D8C31895}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -11604,11 +11646,11 @@
       <c r="A2" s="2">
         <v>1998</v>
       </c>
-      <c r="B2" s="35" cm="1">
+      <c r="B2" s="34" cm="1">
         <f t="array" ref="B2">_xlfn.XLOOKUP(TRUE, Triangle!B5:K5&lt;&gt;"",Triangle!B5:K5, ,0,-1)</f>
         <v>126038</v>
       </c>
-      <c r="C2" s="33" cm="1">
+      <c r="C2" s="32" cm="1">
         <f t="array" ref="C2">_xlfn.XLOOKUP(TRUE, Triangle!B5:K5&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>10</v>
       </c>
@@ -11616,11 +11658,11 @@
         <f>_xlfn.XLOOKUP(C2,Factors!$B$18:$K$18,Factors!$B$20:$K$20, ,0,1)</f>
         <v>1</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="33">
         <f>B2*D2</f>
         <v>126038</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="33">
         <f>E2-B2</f>
         <v>0</v>
       </c>
@@ -11629,11 +11671,11 @@
       <c r="A3" s="2">
         <v>1999</v>
       </c>
-      <c r="B3" s="36" cm="1">
+      <c r="B3" s="35" cm="1">
         <f t="array" ref="B3">_xlfn.XLOOKUP(TRUE, Triangle!B6:K6&lt;&gt;"",Triangle!B6:K6, ,0,-1)</f>
         <v>137247</v>
       </c>
-      <c r="C3" s="30" cm="1">
+      <c r="C3" s="29" cm="1">
         <f t="array" ref="C3">_xlfn.XLOOKUP(TRUE, Triangle!B6:K6&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>9</v>
       </c>
@@ -11641,11 +11683,11 @@
         <f>_xlfn.XLOOKUP(C3,Factors!$B$18:$K$18,Factors!$B$20:$K$20, ,0,1)</f>
         <v>1.00083377669078</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="30">
         <f t="shared" ref="E3:E11" si="0">B3*D3</f>
         <v>137361.43334947948</v>
       </c>
-      <c r="F3" s="31">
+      <c r="F3" s="30">
         <f t="shared" ref="F3:F11" si="1">E3-B3</f>
         <v>114.4333494794846</v>
       </c>
@@ -11654,11 +11696,11 @@
       <c r="A4" s="2">
         <v>2000</v>
       </c>
-      <c r="B4" s="36" cm="1">
+      <c r="B4" s="35" cm="1">
         <f t="array" ref="B4">_xlfn.XLOOKUP(TRUE, Triangle!B7:K7&lt;&gt;"",Triangle!B7:K7, ,0,-1)</f>
         <v>141264</v>
       </c>
-      <c r="C4" s="30" cm="1">
+      <c r="C4" s="29" cm="1">
         <f t="array" ref="C4">_xlfn.XLOOKUP(TRUE, Triangle!B7:K7&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>8</v>
       </c>
@@ -11666,11 +11708,11 @@
         <f>_xlfn.XLOOKUP(C4,Factors!$B$18:$K$18,Factors!$B$20:$K$20, ,0,1)</f>
         <v>1.0018940502358467</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="30">
         <f t="shared" si="0"/>
         <v>141531.56111251665</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="30">
         <f t="shared" si="1"/>
         <v>267.56111251664697</v>
       </c>
@@ -11679,11 +11721,11 @@
       <c r="A5" s="2">
         <v>2001</v>
       </c>
-      <c r="B5" s="36" cm="1">
+      <c r="B5" s="35" cm="1">
         <f t="array" ref="B5">_xlfn.XLOOKUP(TRUE, Triangle!B8:K8&lt;&gt;"",Triangle!B8:K8, ,0,-1)</f>
         <v>141816</v>
       </c>
-      <c r="C5" s="30" cm="1">
+      <c r="C5" s="29" cm="1">
         <f t="array" ref="C5">_xlfn.XLOOKUP(TRUE, Triangle!B8:K8&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>7</v>
       </c>
@@ -11691,11 +11733,11 @@
         <f>_xlfn.XLOOKUP(C5,Factors!$B$18:$K$18,Factors!$B$20:$K$20, ,0,1)</f>
         <v>1.0045793795240048</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <f t="shared" si="0"/>
         <v>142465.42928657625</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <f t="shared" si="1"/>
         <v>649.42928657625453</v>
       </c>
@@ -11704,11 +11746,11 @@
       <c r="A6" s="2">
         <v>2002</v>
       </c>
-      <c r="B6" s="36" cm="1">
+      <c r="B6" s="35" cm="1">
         <f t="array" ref="B6">_xlfn.XLOOKUP(TRUE, Triangle!B9:K9&lt;&gt;"",Triangle!B9:K9, ,0,-1)</f>
         <v>150819</v>
       </c>
-      <c r="C6" s="30" cm="1">
+      <c r="C6" s="29" cm="1">
         <f t="array" ref="C6">_xlfn.XLOOKUP(TRUE, Triangle!B9:K9&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>6</v>
       </c>
@@ -11716,11 +11758,11 @@
         <f>_xlfn.XLOOKUP(C6,Factors!$B$18:$K$18,Factors!$B$20:$K$20, ,0,1)</f>
         <v>1.0080881188123751</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <f t="shared" si="0"/>
         <v>152038.84199116362</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <f t="shared" si="1"/>
         <v>1219.8419911636156</v>
       </c>
@@ -11729,11 +11771,11 @@
       <c r="A7" s="2">
         <v>2003</v>
       </c>
-      <c r="B7" s="36" cm="1">
+      <c r="B7" s="35" cm="1">
         <f t="array" ref="B7">_xlfn.XLOOKUP(TRUE, Triangle!B10:K10&lt;&gt;"",Triangle!B10:K10, ,0,-1)</f>
         <v>154348</v>
       </c>
-      <c r="C7" s="30" cm="1">
+      <c r="C7" s="29" cm="1">
         <f t="array" ref="C7">_xlfn.XLOOKUP(TRUE, Triangle!B10:K10&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>5</v>
       </c>
@@ -11741,11 +11783,11 @@
         <f>_xlfn.XLOOKUP(C7,Factors!$B$18:$K$18,Factors!$B$20:$K$20, ,0,1)</f>
         <v>1.0184817328136455</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <f t="shared" si="0"/>
         <v>157200.61849632056</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <f t="shared" si="1"/>
         <v>2852.6184963205596</v>
       </c>
@@ -11754,11 +11796,11 @@
       <c r="A8" s="2">
         <v>2004</v>
       </c>
-      <c r="B8" s="36" cm="1">
+      <c r="B8" s="35" cm="1">
         <f t="array" ref="B8">_xlfn.XLOOKUP(TRUE, Triangle!B11:K11&lt;&gt;"",Triangle!B11:K11, ,0,-1)</f>
         <v>170055</v>
       </c>
-      <c r="C8" s="30" cm="1">
+      <c r="C8" s="29" cm="1">
         <f t="array" ref="C8">_xlfn.XLOOKUP(TRUE, Triangle!B11:K11&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>4</v>
       </c>
@@ -11766,11 +11808,11 @@
         <f>_xlfn.XLOOKUP(C8,Factors!$B$18:$K$18,Factors!$B$20:$K$20, ,0,1)</f>
         <v>1.0381309634190656</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <f t="shared" si="0"/>
         <v>176539.36098422922</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <f t="shared" si="1"/>
         <v>6484.3609842292208</v>
       </c>
@@ -11779,11 +11821,11 @@
       <c r="A9" s="2">
         <v>2005</v>
       </c>
-      <c r="B9" s="36" cm="1">
+      <c r="B9" s="35" cm="1">
         <f t="array" ref="B9">_xlfn.XLOOKUP(TRUE, Triangle!B12:K12&lt;&gt;"",Triangle!B12:K12, ,0,-1)</f>
         <v>165521</v>
       </c>
-      <c r="C9" s="30" cm="1">
+      <c r="C9" s="29" cm="1">
         <f t="array" ref="C9">_xlfn.XLOOKUP(TRUE, Triangle!B12:K12&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>3</v>
       </c>
@@ -11791,11 +11833,11 @@
         <f>_xlfn.XLOOKUP(C9,Factors!$B$18:$K$18,Factors!$B$20:$K$20, ,0,1)</f>
         <v>1.0906355135896715</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <f t="shared" si="0"/>
         <v>180523.08084487601</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <f t="shared" si="1"/>
         <v>15002.080844876007</v>
       </c>
@@ -11804,11 +11846,11 @@
       <c r="A10" s="2">
         <v>2006</v>
       </c>
-      <c r="B10" s="36" cm="1">
+      <c r="B10" s="35" cm="1">
         <f t="array" ref="B10">_xlfn.XLOOKUP(TRUE, Triangle!B13:K13&lt;&gt;"",Triangle!B13:K13, ,0,-1)</f>
         <v>140342</v>
       </c>
-      <c r="C10" s="30" cm="1">
+      <c r="C10" s="29" cm="1">
         <f t="array" ref="C10">_xlfn.XLOOKUP(TRUE, Triangle!B13:K13&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>2</v>
       </c>
@@ -11816,11 +11858,11 @@
         <f>_xlfn.XLOOKUP(C10,Factors!$B$18:$K$18,Factors!$B$20:$K$20, ,0,1)</f>
         <v>1.1998717474005061</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <f t="shared" si="0"/>
         <v>168392.40077368182</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <f t="shared" si="1"/>
         <v>28050.400773681817</v>
       </c>
@@ -11829,11 +11871,11 @@
       <c r="A11" s="2">
         <v>2007</v>
       </c>
-      <c r="B11" s="39" cm="1">
+      <c r="B11" s="37" cm="1">
         <f t="array" ref="B11">_xlfn.XLOOKUP(TRUE, Triangle!B14:K14&lt;&gt;"",Triangle!B14:K14, ,0,-1)</f>
         <v>106588</v>
       </c>
-      <c r="C11" s="40" cm="1">
+      <c r="C11" s="38" cm="1">
         <f t="array" ref="C11">_xlfn.XLOOKUP(TRUE, Triangle!B14:K14&lt;&gt;"", Triangle!$B$4:$K$4, , 0, -1)</f>
         <v>1</v>
       </c>
@@ -11841,30 +11883,30 @@
         <f>_xlfn.XLOOKUP(C11,Factors!$B$18:$K$18,Factors!$B$20:$K$20, ,0,1)</f>
         <v>1.8612806079549675</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="39">
         <f t="shared" si="0"/>
         <v>198390.17744070408</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="39">
         <f t="shared" si="1"/>
         <v>91802.177440704079</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="41">
         <f>SUM(B2:B11)</f>
         <v>1434038</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="34">
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="43">
         <f>SUM(E2:E11)</f>
         <v>1580480.9042795475</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="43">
         <f>SUM(F2:F11)</f>
         <v>146442.90427954769</v>
       </c>
@@ -11888,29 +11930,32 @@
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="34">
         <f>'Chain Ladder'!F12</f>
         <v>146098.34965261447</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="37">
+      <c r="B17" s="36">
         <f>F12</f>
         <v>146442.90427954769</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="30">
         <f>(B17-B16)</f>
         <v>344.55462693321169</v>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="48">
         <f>(B17-B16)/B16</f>
         <v>2.3583745316252845E-3</v>
       </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="67"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12145,16 +12190,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{467D82E0-BE4A-49AD-B937-5963BEE123AF}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="0de0ad09-d942-493f-8a46-fed7b7171831"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="bb7f4c9e-7d23-4406-8c0b-272a3f04c51d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="0de0ad09-d942-493f-8a46-fed7b7171831"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
